--- a/SGC-CKN/Excel/95118063-57b2-44e3-9db8-ac656fb1a54e_Đại_trà_P11_128_D800_21-04-2026.xlsx
+++ b/SGC-CKN/Excel/95118063-57b2-44e3-9db8-ac656fb1a54e_Đại_trà_P11_128_D800_21-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>10:00 21/04/2026</t>
+    <t>10:00 02/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>17:32 21/04/2026</t>
+    <t>17:32 02/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">10:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">10:30
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>Chiều dài lớp không ghi rõ, tự tính từ 0 đến 11m</t>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t/>
@@ -129,7 +129,7 @@
   </si>
   <si>
     <t xml:space="preserve">12:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -139,7 +139,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -149,7 +149,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:30
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -159,7 +159,7 @@
   </si>
   <si>
     <t xml:space="preserve">14:00
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -169,7 +169,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:23
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>Chạm sỏi tại cao độ 49.50</t>
@@ -182,7 +182,7 @@
   </si>
   <si>
     <t xml:space="preserve">17:32
-21/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>

--- a/SGC-CKN/Excel/95118063-57b2-44e3-9db8-ac656fb1a54e_Đại_trà_P11_128_D800_21-04-2026.xlsx
+++ b/SGC-CKN/Excel/95118063-57b2-44e3-9db8-ac656fb1a54e_Đại_trà_P11_128_D800_21-04-2026.xlsx
@@ -219,7 +219,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -292,12 +292,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -308,7 +302,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,11 +346,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
       </patternFill>
     </fill>
@@ -377,12 +366,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5F3FC"/>
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
+        <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -478,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -522,44 +511,44 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -570,16 +559,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1168,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-11</v>
+        <v>-3.8</v>
       </c>
       <c r="H11" s="5">
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="J11" s="8">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1200,19 +1186,19 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-11</v>
+        <v>-3.8</v>
       </c>
       <c r="G12" s="9">
-        <v>-13.8</v>
+        <v>-12.6</v>
       </c>
       <c r="H12" s="9">
         <v>0.5</v>
       </c>
       <c r="I12" s="9">
-        <v>2.8</v>
+        <v>8.8</v>
       </c>
       <c r="J12" s="8">
-        <v>5.6</v>
+        <v>17.6</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>34</v>
@@ -1235,161 +1221,161 @@
         <v>37</v>
       </c>
       <c r="F13" s="12">
-        <v>-13.8</v>
+        <v>-12.6</v>
       </c>
       <c r="G13" s="12">
-        <v>-18.6</v>
+        <v>-18.8</v>
       </c>
       <c r="H13" s="12">
         <v>1</v>
       </c>
       <c r="I13" s="12">
-        <v>4.8</v>
-      </c>
-      <c r="J13" s="15">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>6.2</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="16">
-        <v>-18.6</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="15">
+        <v>-18.8</v>
+      </c>
+      <c r="G14" s="15">
         <v>-28.2</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>1</v>
       </c>
-      <c r="I14" s="16">
-        <v>9.6</v>
+      <c r="I14" s="15">
+        <v>9.4</v>
       </c>
       <c r="J14" s="8">
-        <v>9.6</v>
-      </c>
-      <c r="K14" s="17" t="s">
+        <v>9.4</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>-28.2</v>
       </c>
-      <c r="G15" s="19">
-        <v>-35.4</v>
-      </c>
-      <c r="H15" s="19">
+      <c r="G15" s="18">
+        <v>-35.1</v>
+      </c>
+      <c r="H15" s="18">
         <v>0.5</v>
       </c>
-      <c r="I15" s="19">
-        <v>7.2</v>
+      <c r="I15" s="18">
+        <v>6.9</v>
       </c>
       <c r="J15" s="8">
-        <v>14.4</v>
-      </c>
-      <c r="K15" s="20" t="s">
+        <v>13.8</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="22">
-        <v>-35.4</v>
-      </c>
-      <c r="G16" s="22">
+      <c r="F16" s="21">
+        <v>-35.1</v>
+      </c>
+      <c r="G16" s="21">
         <v>-38.2</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>0.5</v>
       </c>
-      <c r="I16" s="22">
-        <v>2.8</v>
+      <c r="I16" s="21">
+        <v>3.1</v>
       </c>
       <c r="J16" s="8">
-        <v>5.6</v>
-      </c>
-      <c r="K16" s="23" t="s">
+        <v>6.2</v>
+      </c>
+      <c r="K16" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>-38.2</v>
       </c>
-      <c r="G17" s="25">
-        <v>-49.5</v>
-      </c>
-      <c r="H17" s="25">
+      <c r="G17" s="24">
+        <v>-44.5</v>
+      </c>
+      <c r="H17" s="24">
         <v>1.38</v>
       </c>
-      <c r="I17" s="25">
-        <v>11.3</v>
-      </c>
-      <c r="J17" s="8">
-        <v>8.17</v>
-      </c>
-      <c r="K17" s="26" t="s">
+      <c r="I17" s="24">
+        <v>6.3</v>
+      </c>
+      <c r="J17" s="27">
+        <v>4.55</v>
+      </c>
+      <c r="K17" s="25" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1410,7 +1396,7 @@
         <v>53</v>
       </c>
       <c r="F18" s="28">
-        <v>-49.5</v>
+        <v>-44.5</v>
       </c>
       <c r="G18" s="28">
         <v>-49.86</v>
@@ -1419,29 +1405,29 @@
         <v>2.15</v>
       </c>
       <c r="I18" s="28">
-        <v>0.36</v>
-      </c>
-      <c r="J18" s="31">
-        <v>0.17</v>
+        <v>5.36</v>
+      </c>
+      <c r="J18" s="27">
+        <v>2.49</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1580,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-11</v>
+        <v>-3.8</v>
       </c>
       <c r="G2" s="5">
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="I2" s="8">
-        <v>22</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1606,19 +1592,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-11</v>
+        <v>-3.8</v>
       </c>
       <c r="F3" s="9">
-        <v>-13.8</v>
+        <v>-12.6</v>
       </c>
       <c r="G3" s="9">
         <v>0.5</v>
       </c>
       <c r="H3" s="9">
-        <v>2.8</v>
+        <v>8.8</v>
       </c>
       <c r="I3" s="8">
-        <v>5.6</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1635,135 +1621,135 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-13.8</v>
+        <v>-12.6</v>
       </c>
       <c r="F4" s="12">
-        <v>-18.6</v>
+        <v>-18.8</v>
       </c>
       <c r="G4" s="12">
         <v>1</v>
       </c>
       <c r="H4" s="12">
-        <v>4.8</v>
-      </c>
-      <c r="I4" s="15">
-        <v>4.8</v>
+        <v>6.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-18.6</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>-18.8</v>
+      </c>
+      <c r="F5" s="15">
         <v>-28.2</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>1</v>
       </c>
-      <c r="H5" s="16">
-        <v>9.6</v>
+      <c r="H5" s="15">
+        <v>9.4</v>
       </c>
       <c r="I5" s="8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-28.2</v>
       </c>
-      <c r="F6" s="19">
-        <v>-35.4</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="F6" s="18">
+        <v>-35.1</v>
+      </c>
+      <c r="G6" s="18">
         <v>0.5</v>
       </c>
-      <c r="H6" s="19">
-        <v>7.2</v>
+      <c r="H6" s="18">
+        <v>6.9</v>
       </c>
       <c r="I6" s="8">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
-        <v>-35.4</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="E7" s="21">
+        <v>-35.1</v>
+      </c>
+      <c r="F7" s="21">
         <v>-38.2</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>0.5</v>
       </c>
-      <c r="H7" s="22">
-        <v>2.8</v>
+      <c r="H7" s="21">
+        <v>3.1</v>
       </c>
       <c r="I7" s="8">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="24">
         <v>-38.2</v>
       </c>
-      <c r="F8" s="25">
-        <v>-49.5</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="F8" s="24">
+        <v>-44.5</v>
+      </c>
+      <c r="G8" s="24">
         <v>1.38</v>
       </c>
-      <c r="H8" s="25">
-        <v>11.3</v>
-      </c>
-      <c r="I8" s="8">
-        <v>8.17</v>
+      <c r="H8" s="24">
+        <v>6.3</v>
+      </c>
+      <c r="I8" s="27">
+        <v>4.55</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1780,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-49.5</v>
+        <v>-44.5</v>
       </c>
       <c r="F9" s="28">
         <v>-49.86</v>
@@ -1789,38 +1775,38 @@
         <v>2.15</v>
       </c>
       <c r="H9" s="28">
-        <v>0.36</v>
-      </c>
-      <c r="I9" s="31">
-        <v>0.17</v>
+        <v>5.36</v>
+      </c>
+      <c r="I9" s="27">
+        <v>2.49</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="33">
         <v>-49.86</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="33">
         <v>7.53</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="33">
         <v>49.86</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="33">
         <v>6.62</v>
       </c>
     </row>
